--- a/nino/PANADERIA/Estructura_Costos_Panaderia_NINO.xlsx
+++ b/nino/PANADERIA/Estructura_Costos_Panaderia_NINO.xlsx
@@ -20,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="9">
     <font>
       <name val="Calibri"/>
@@ -142,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -165,27 +167,54 @@
     <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -565,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -629,8 +658,9 @@
           <t>VENTAS BRUTAS (con IVA)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>35523669</v>
+      <c r="B6" s="6">
+        <f>B8*1.21</f>
+        <v/>
       </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
@@ -650,8 +680,9 @@
           <t>(-) IVA Debito Fiscal</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>-6165265</v>
+      <c r="B7" s="6">
+        <f>-B8*0.21</f>
+        <v/>
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
@@ -748,13 +779,13 @@
           <t>COSTO TOTAL INSUMOS</t>
         </is>
       </c>
-      <c r="B14" s="11" t="n">
-        <v>-8807521</v>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
+      <c r="B14" s="11">
+        <f>-B8*0.30000000000000004</f>
+        <v/>
+      </c>
+      <c r="C14" s="12">
+        <f>ABS(B14)/B8</f>
+        <v/>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -773,7 +804,7 @@
           <t xml:space="preserve">  Facturas y medialunas</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>-3272484</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -798,7 +829,7 @@
           <t xml:space="preserve">  Panes</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>-4291445</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -823,7 +854,7 @@
           <t xml:space="preserve">  Pre-pizzas y pizzetas</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>-602637</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -848,7 +879,7 @@
           <t xml:space="preserve">  Bizcochuelos y dulces</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>-406024</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -873,7 +904,7 @@
           <t xml:space="preserve">  Discos y tapas</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>-189365</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -898,7 +929,7 @@
           <t xml:space="preserve">  Pan rallado y derivados</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -923,7 +954,7 @@
           <t xml:space="preserve">  Otros elaborados</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>-45566</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -948,18 +979,19 @@
           <t>MARGEN BRUTO</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n">
-        <v>20550883</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
+      <c r="B22" s="8">
+        <f>B8+B14</f>
+        <v/>
+      </c>
+      <c r="C22" s="15">
+        <f>B22/B8</f>
+        <v/>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7">
-        <f> Ventas - CMV</f>
-        <v/>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Ventas - CMV</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1004,15 +1036,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>3.1 SUELDOS Y CARGAS SOCIALES</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr"/>
-      <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="14" t="inlineStr"/>
+      <c r="B27" s="16" t="inlineStr"/>
+      <c r="C27" s="16" t="inlineStr"/>
+      <c r="D27" s="16" t="inlineStr"/>
+      <c r="E27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1020,13 +1052,13 @@
           <t>Sueldos brutos (3 empleados)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>-3540822</v>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
+      <c r="B28" s="6">
+        <f>B29+B30</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>ABS(B28)/B8</f>
+        <v/>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
@@ -1045,7 +1077,7 @@
           <t xml:space="preserve">  - Remunerativo</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="13" t="n">
         <v>-3240822</v>
       </c>
       <c r="C29" s="9" t="inlineStr"/>
@@ -1066,7 +1098,7 @@
           <t xml:space="preserve">  - No Remunerativo</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="13" t="n">
         <v>-300000</v>
       </c>
       <c r="C30" s="9" t="inlineStr"/>
@@ -1087,13 +1119,13 @@
           <t>Contribuciones patronales (F.930)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>-963820</v>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
+      <c r="B31" s="6">
+        <f>B29*0.2974</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>ABS(B31)/B8</f>
+        <v/>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
@@ -1112,8 +1144,9 @@
           <t xml:space="preserve">  - Jubilacion (SIPA)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
-        <v>-411908</v>
+      <c r="B32" s="13">
+        <f>B29*0.1271</f>
+        <v/>
       </c>
       <c r="C32" s="9" t="inlineStr"/>
       <c r="D32" s="9" t="inlineStr">
@@ -1133,8 +1166,9 @@
           <t xml:space="preserve">  - PAMI (Ley 19.032)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>-51205</v>
+      <c r="B33" s="13">
+        <f>B29*0.0158</f>
+        <v/>
       </c>
       <c r="C33" s="9" t="inlineStr"/>
       <c r="D33" s="9" t="inlineStr">
@@ -1150,8 +1184,9 @@
           <t xml:space="preserve">  - Asignaciones Familiares</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
-        <v>-180190</v>
+      <c r="B34" s="13">
+        <f>B29*0.0556</f>
+        <v/>
       </c>
       <c r="C34" s="9" t="inlineStr"/>
       <c r="D34" s="9" t="inlineStr">
@@ -1167,8 +1202,9 @@
           <t xml:space="preserve">  - Fondo Nacional de Empleo</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
-        <v>-28843</v>
+      <c r="B35" s="13">
+        <f>B29*0.0089</f>
+        <v/>
       </c>
       <c r="C35" s="9" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr">
@@ -1184,8 +1220,9 @@
           <t xml:space="preserve">  - Obra Social patronal</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
-        <v>-194449</v>
+      <c r="B36" s="13">
+        <f>B29*0.06</f>
+        <v/>
       </c>
       <c r="C36" s="9" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
@@ -1201,8 +1238,9 @@
           <t xml:space="preserve">  - ART (estimado)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
-        <v>-97225</v>
+      <c r="B37" s="13">
+        <f>B29*0.03</f>
+        <v/>
       </c>
       <c r="C37" s="9" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
@@ -1222,13 +1260,13 @@
           <t>SAC proporcional (1/12)</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
-        <v>-350387</v>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
+      <c r="B38" s="6">
+        <f>(B29+B31)/12</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>ABS(B38)/B8</f>
+        <v/>
       </c>
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr">
@@ -1243,7 +1281,7 @@
           <t>Seguro Vida Obligatorio</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>-1500</v>
       </c>
       <c r="C39" s="9" t="inlineStr"/>
@@ -1259,32 +1297,32 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>SUBTOTAL LABORAL</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>-4856529</v>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>16.5%</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr"/>
-      <c r="E40" s="15" t="inlineStr"/>
+      <c r="B40" s="19">
+        <f>B28+B31+B38+B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="20">
+        <f>ABS(B40)/B8</f>
+        <v/>
+      </c>
+      <c r="D40" s="18" t="inlineStr"/>
+      <c r="E40" s="18" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>3.2 SERVICIOS (prorrateo panaderia)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr"/>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="14" t="inlineStr"/>
-      <c r="E42" s="14" t="inlineStr"/>
+      <c r="B42" s="16" t="inlineStr"/>
+      <c r="C42" s="16" t="inlineStr"/>
+      <c r="D42" s="16" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1295,10 +1333,9 @@
       <c r="B43" s="6" t="n">
         <v>-515550</v>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
+      <c r="C43" s="17">
+        <f>ABS(B43)/B8</f>
+        <v/>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -1342,10 +1379,9 @@
       <c r="B46" s="6" t="n">
         <v>-402339</v>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
+      <c r="C46" s="17">
+        <f>ABS(B46)/B8</f>
+        <v/>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -1381,900 +1417,799 @@
       <c r="E48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>SUBTOTAL SERVICIOS</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>-917889</v>
-      </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>3.1%</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr"/>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="B49" s="19">
+        <f>B43+B46</f>
+        <v/>
+      </c>
+      <c r="C49" s="20">
+        <f>ABS(B49)/B8</f>
+        <v/>
+      </c>
+      <c r="D49" s="18" t="inlineStr"/>
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>Basado en facturas reales Feb-Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>3.3 OTROS COSTOS FIJOS (estimados)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr"/>
-      <c r="C51" s="14" t="inlineStr"/>
-      <c r="D51" s="14" t="inlineStr"/>
-      <c r="E51" s="14" t="inlineStr"/>
+      <c r="B51" s="16" t="inlineStr"/>
+      <c r="C51" s="16" t="inlineStr"/>
+      <c r="D51" s="16" t="inlineStr"/>
+      <c r="E51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Alquiler / amort. inmueble (prorrateo)</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="n">
-        <v>-300000</v>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr"/>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>~25% m2 panaderia s/total local. AJUSTAR</t>
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Descartables / packaging</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="C52" s="23">
+        <f>ABS(B52)/B8</f>
+        <v/>
+      </c>
+      <c r="D52" s="21" t="inlineStr"/>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>Bolsas papel, nylon, cajas tortas, film, bandejas</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Descartables / packaging</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="n">
-        <v>-120000</v>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr"/>
-      <c r="E53" s="17" t="inlineStr">
-        <is>
-          <t>Bolsas papel, nylon, cajas tortas, film, bandejas</t>
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Mantenimiento equipos</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="C53" s="23">
+        <f>ABS(B53)/B8</f>
+        <v/>
+      </c>
+      <c r="D53" s="21" t="inlineStr"/>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>Service horno industrial, amasadora, heladeras, repuestos</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Amortizacion equipos</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr"/>
-      <c r="E54" s="17" t="inlineStr">
-        <is>
-          <t>Horno industrial+amasadora+sobadora+batidora+fermentadora (~$45M/60m)</t>
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Indumentaria / EPP</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="C54" s="23">
+        <f>ABS(B54)/B8</f>
+        <v/>
+      </c>
+      <c r="D54" s="21" t="inlineStr"/>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Delantales, gorros, guantes (3 empleados)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Mantenimiento equipos</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="n">
-        <v>-60000</v>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr"/>
-      <c r="E55" s="17" t="inlineStr">
-        <is>
-          <t>Service horno industrial, amasadora, heladeras, repuestos</t>
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Habilitacion bromatologica</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n">
+        <v>-12000</v>
+      </c>
+      <c r="C55" s="23">
+        <f>ABS(B55)/B8</f>
+        <v/>
+      </c>
+      <c r="D55" s="21" t="inlineStr"/>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>Anual / 12. Obligatoria elaboracion alimentos</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Seguros (incendio, RC)</t>
-        </is>
-      </c>
-      <c r="B56" s="18" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr"/>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>Prorrateo por m2 panaderia</t>
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Habilitacion municipal</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="C56" s="23">
+        <f>ABS(B56)/B8</f>
+        <v/>
+      </c>
+      <c r="D56" s="21" t="inlineStr"/>
+      <c r="E56" s="21" t="inlineStr">
+        <is>
+          <t>Tasa comercio Lujan de Cuyo / 12</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Indumentaria / EPP</t>
-        </is>
-      </c>
-      <c r="B57" s="18" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr"/>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Delantales, gorros, guantes (3 empleados)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Agua (prorrateo)</t>
-        </is>
-      </c>
-      <c r="B58" s="18" t="n">
-        <v>-25000</v>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr"/>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Limpieza, amasado, produccion</t>
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>SUBTOTAL OTROS FIJOS</t>
+        </is>
+      </c>
+      <c r="B57" s="19">
+        <f>SUM(B52:B56)</f>
+        <v/>
+      </c>
+      <c r="C57" s="20">
+        <f>ABS(B57)/B8</f>
+        <v/>
+      </c>
+      <c r="D57" s="18" t="inlineStr"/>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>Estimados - ajustar con datos reales</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Habilitacion bromatologica</t>
-        </is>
-      </c>
-      <c r="B59" s="18" t="n">
-        <v>-12000</v>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr"/>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>Anual / 12. Obligatoria elaboracion alimentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Habilitacion municipal</t>
-        </is>
-      </c>
-      <c r="B60" s="18" t="n">
-        <v>-8000</v>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr"/>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t>Tasa comercio Lujan de Cuyo / 12</t>
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="B59" s="11">
+        <f>B40+B49+B57</f>
+        <v/>
+      </c>
+      <c r="C59" s="12">
+        <f>ABS(B59)/B8</f>
+        <v/>
+      </c>
+      <c r="D59" s="10" t="inlineStr"/>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>Laboral + Servicios + Otros</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
-        <is>
-          <t>SUBTOTAL OTROS FIJOS</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="n">
-        <v>-730000</v>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr"/>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>Estimados - ajustar con datos reales</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>4. COSTOS VARIABLES (% sobre ventas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Monto Mensual ($)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>% s/Ventas</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Tasa/Base</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL COSTOS FIJOS</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="n">
-        <v>-6504418</v>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="inlineStr"/>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Laboral + Servicios + Otros (estimados)</t>
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>4.1 COMISIONES TARJETAS</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr"/>
+      <c r="C63" s="16" t="inlineStr"/>
+      <c r="D63" s="16" t="inlineStr"/>
+      <c r="E63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta Credito (14.3% ventas)</t>
+        </is>
+      </c>
+      <c r="B64" s="6">
+        <f>-B8*0.142708*0.03</f>
+        <v/>
+      </c>
+      <c r="C64" s="24">
+        <f>ABS(B64)/B8</f>
+        <v/>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Naranja 41%, Visa 41%, MC 15%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>4. COSTOS VARIABLES (% sobre ventas)</t>
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta Debito (24.0% ventas)</t>
+        </is>
+      </c>
+      <c r="B65" s="6">
+        <f>-B8*0.240486*0.012</f>
+        <v/>
+      </c>
+      <c r="C65" s="24">
+        <f>ABS(B65)/B8</f>
+        <v/>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Visa 64%, Mastercard 36%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Monto Mensual ($)</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>% s/Ventas</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Tasa/Base</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>Notas</t>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Billetera Virtual (14.9% ventas)</t>
+        </is>
+      </c>
+      <c r="B66" s="6">
+        <f>-B8*0.149097*0.015</f>
+        <v/>
+      </c>
+      <c r="C66" s="24">
+        <f>ABS(B66)/B8</f>
+        <v/>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Mercado Pago y otras</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>4.1 COMISIONES TARJETAS</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr"/>
-      <c r="C67" s="14" t="inlineStr"/>
-      <c r="D67" s="14" t="inlineStr"/>
-      <c r="E67" s="14" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>Tarjeta Credito (14.3% ventas)</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>-125690</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>0.43%</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Naranja 41%, Visa 41%, MC 15%</t>
-        </is>
-      </c>
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>Subtotal comisiones</t>
+        </is>
+      </c>
+      <c r="B67" s="26">
+        <f>B64+B65+B66</f>
+        <v/>
+      </c>
+      <c r="C67" s="27">
+        <f>ABS(B67)/B8</f>
+        <v/>
+      </c>
+      <c r="D67" s="25" t="inlineStr"/>
+      <c r="E67" s="25" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Tarjeta Debito (24.0% ventas)</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>-84723</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>Visa 64%, Mastercard 36%</t>
-        </is>
-      </c>
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>4.2 IMPUESTOS OPERATIVOS</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr"/>
+      <c r="C69" s="16" t="inlineStr"/>
+      <c r="D69" s="16" t="inlineStr"/>
+      <c r="E69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Billetera Virtual (14.9% ventas)</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n">
-        <v>-65659</v>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>0.22%</t>
-        </is>
+          <t>Ingresos Brutos (Mendoza)</t>
+        </is>
+      </c>
+      <c r="B70" s="6">
+        <f>-B8*0.03</f>
+        <v/>
+      </c>
+      <c r="C70" s="17">
+        <f>ABS(B70)/B8</f>
+        <v/>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Mercado Pago y otras</t>
+          <t>Ley Impositiva Mza 2026, Rubro 7 comercio minorista</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>Subtotal comisiones</t>
-        </is>
-      </c>
-      <c r="B71" s="20" t="n">
-        <v>-276072</v>
-      </c>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>0.94%</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr"/>
-      <c r="E71" s="19" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>4.2 IMPUESTOS OPERATIVOS</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="inlineStr"/>
-      <c r="C73" s="14" t="inlineStr"/>
-      <c r="D73" s="14" t="inlineStr"/>
-      <c r="E73" s="14" t="inlineStr"/>
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Imp. Debitos y Creditos Bancarios</t>
+        </is>
+      </c>
+      <c r="B71" s="6">
+        <f>-B8*0.532291*0.012</f>
+        <v/>
+      </c>
+      <c r="C71" s="24">
+        <f>ABS(B71)/B8</f>
+        <v/>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>1.2% s/banc.</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Ley 25.413. Solo s/bancarizado (53.2% ventas, excluye efectivo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="25" t="inlineStr">
+        <is>
+          <t>Subtotal impuestos</t>
+        </is>
+      </c>
+      <c r="B72" s="26">
+        <f>B70+B71</f>
+        <v/>
+      </c>
+      <c r="C72" s="28">
+        <f>ABS(B72)/B8</f>
+        <v/>
+      </c>
+      <c r="D72" s="25" t="inlineStr"/>
+      <c r="E72" s="25" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Ingresos Brutos (Mendoza)</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>-880752</v>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Ley Impositiva Mza 2026, Rubro 7 comercio minorista</t>
-        </is>
-      </c>
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>4.3 MERMA / DESCARTE</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr"/>
+      <c r="C74" s="16" t="inlineStr"/>
+      <c r="D74" s="16" t="inlineStr"/>
+      <c r="E74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Imp. Debitos y Creditos Bancarios</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>-187526</v>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>0.64%</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>1.2% s/banc.</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Ley 25.413. Solo s/bancarizado (53.2% ventas, excluye efectivo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
-        <is>
-          <t>Subtotal impuestos</t>
-        </is>
-      </c>
-      <c r="B76" s="20" t="n">
-        <v>-1068278</v>
-      </c>
-      <c r="C76" s="19" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="D76" s="19" t="inlineStr"/>
-      <c r="E76" s="19" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>4.3 MERMA / DESCARTE</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr"/>
-      <c r="C78" s="14" t="inlineStr"/>
-      <c r="D78" s="14" t="inlineStr"/>
-      <c r="E78" s="14" t="inlineStr"/>
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>Merma estimada</t>
+        </is>
+      </c>
+      <c r="B75" s="22">
+        <f>-B8*0.04</f>
+        <v/>
+      </c>
+      <c r="C75" s="23">
+        <f>ABS(B75)/B8</f>
+        <v/>
+      </c>
+      <c r="D75" s="21" t="inlineStr"/>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t>Panaderia tipico 3-5% (pan del dia, vida util corta). AJUSTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS VARIABLES</t>
+        </is>
+      </c>
+      <c r="B77" s="11">
+        <f>B67+B72+B75</f>
+        <v/>
+      </c>
+      <c r="C77" s="12">
+        <f>ABS(B77)/B8</f>
+        <v/>
+      </c>
+      <c r="D77" s="10" t="inlineStr"/>
+      <c r="E77" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="inlineStr">
-        <is>
-          <t>Merma estimada</t>
-        </is>
-      </c>
-      <c r="B79" s="18" t="n">
-        <v>-1174336</v>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="inlineStr"/>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>Panaderia tipico 3-5% (pan del dia, vida util corta). AJUSTAR</t>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>5. RESULTADO - MARGEN DE CONTRIBUCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Monto Mensual ($)</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>% s/Ventas</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>TOTAL COSTOS VARIABLES</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="n">
-        <v>-2518686</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>8.6%</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="inlineStr"/>
-      <c r="E81" s="10" t="inlineStr"/>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Ventas Netas</t>
+        </is>
+      </c>
+      <c r="B81" s="6">
+        <f>B8</f>
+        <v/>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>(-) CMV</t>
+        </is>
+      </c>
+      <c r="B82" s="6">
+        <f>B14</f>
+        <v/>
+      </c>
+      <c r="C82" s="17">
+        <f>ABS(B82)/B81</f>
+        <v/>
+      </c>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>5. RESULTADO - MARGEN DE CONTRIBUCION</t>
-        </is>
-      </c>
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>MARGEN BRUTO</t>
+        </is>
+      </c>
+      <c r="B83" s="26">
+        <f>B81+B82</f>
+        <v/>
+      </c>
+      <c r="C83" s="28">
+        <f>B83/B81</f>
+        <v/>
+      </c>
+      <c r="D83" s="25" t="inlineStr"/>
+      <c r="E83" s="25" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>Monto Mensual ($)</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>% s/Ventas</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr"/>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Notas</t>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>(-) Costos Fijos</t>
+        </is>
+      </c>
+      <c r="B84" s="6">
+        <f>B59</f>
+        <v/>
+      </c>
+      <c r="C84" s="17">
+        <f>ABS(B84)/B81</f>
+        <v/>
+      </c>
+      <c r="D84" s="5" t="inlineStr"/>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Laboral + Servicios + Otros</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>Ventas Netas</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="n">
-        <v>29358404</v>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
+          <t>(-) Costos Variables</t>
+        </is>
+      </c>
+      <c r="B85" s="6">
+        <f>B77</f>
+        <v/>
+      </c>
+      <c r="C85" s="17">
+        <f>ABS(B85)/B81</f>
+        <v/>
       </c>
       <c r="D85" s="5" t="inlineStr"/>
       <c r="E85" s="5" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>(-) CMV</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="n">
-        <v>-8807521</v>
-      </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr"/>
-      <c r="E86" s="5" t="inlineStr"/>
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t>RESULTADO NETO</t>
+        </is>
+      </c>
+      <c r="B86" s="30">
+        <f>B83+B84+B85</f>
+        <v/>
+      </c>
+      <c r="C86" s="31">
+        <f>B86/B81</f>
+        <v/>
+      </c>
+      <c r="D86" s="29" t="inlineStr"/>
+      <c r="E86" s="29" t="inlineStr">
+        <is>
+          <t>SUPERAVITARIO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="19">
-        <f> MARGEN BRUTO</f>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Items en amarillo son estimados. Ajustar con datos reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>6. PUNTO DE EQUILIBRIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="25" t="inlineStr">
+        <is>
+          <t>Ventas necesarias para cubrir costos fijos (margen 70%)</t>
+        </is>
+      </c>
+      <c r="B90" s="26">
+        <f>-B59/(0.7+B77/B8)</f>
         <v/>
       </c>
-      <c r="B87" s="20" t="n">
-        <v>20550883</v>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="D87" s="19" t="inlineStr"/>
-      <c r="E87" s="19" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>(-) Costos Fijos</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="n">
-        <v>-6504418</v>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr"/>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>Laboral + Servicios + Otros</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>(-) Costos Variables</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="n">
-        <v>-2518686</v>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>8.6%</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr"/>
-      <c r="E89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="21">
-        <f> MARGEN DE CONTRIBUCION</f>
+      <c r="C90" s="25" t="inlineStr"/>
+      <c r="D90" s="25" t="inlineStr"/>
+      <c r="E90" s="25" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Ventas actuales promedio</t>
+        </is>
+      </c>
+      <c r="B91" s="6">
+        <f>B8</f>
         <v/>
       </c>
-      <c r="B90" s="22" t="n">
-        <v>11527779</v>
-      </c>
-      <c r="C90" s="21" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="D90" s="21" t="inlineStr"/>
-      <c r="E90" s="21" t="inlineStr">
-        <is>
-          <t>SUPERAVITARIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Items en amarillo son estimados. Ajustar con datos reales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>6. PUNTO DE EQUILIBRIO</t>
+      <c r="C91" s="5" t="inlineStr"/>
+      <c r="D91" s="5" t="inlineStr"/>
+      <c r="E91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Cobertura punto de equilibrio</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr"/>
+      <c r="C92" s="15">
+        <f>B91/B90</f>
+        <v/>
+      </c>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>OK - cubre costos fijos</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="19" t="inlineStr">
-        <is>
-          <t>Ventas necesarias para cubrir costos fijos (margen 70%)</t>
-        </is>
-      </c>
-      <c r="B94" s="20" t="n">
-        <v>10589909</v>
-      </c>
-      <c r="C94" s="19" t="inlineStr"/>
-      <c r="D94" s="19" t="inlineStr"/>
-      <c r="E94" s="19" t="inlineStr"/>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>SUPUESTOS</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="inlineStr">
-        <is>
-          <t>Ventas actuales promedio</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="n">
-        <v>29358404</v>
-      </c>
-      <c r="C95" s="5" t="inlineStr"/>
-      <c r="D95" s="5" t="inlineStr"/>
-      <c r="E95" s="5" t="inlineStr"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1. Empresa NO inscripta como MiPyME - Contribuciones patronales SUSS al 20.74%</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>Cobertura punto de equilibrio</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr"/>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>277%</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr"/>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>OK - cubre costos fijos</t>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2. CCT 130/75 Empleados de Comercio - Categoria Auxiliar Especializado A, sin antiguedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3. Sueldo: $1,080,274 remunerativo + $100,000 NR = $1,180,274/empleado (escala Dic 2025 - Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>SUPUESTOS</t>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Contribuciones patronales (29.74%) calculadas SOLO sobre remunerativo. NR no genera cargas</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. Empresa NO inscripta como MiPyME - Contribuciones patronales SUSS al 20.4% (si obtiene certificado MiPyME baja a 18%)</t>
+          <t xml:space="preserve">  5. SAC mensualizado sobre base remunerativa + contribuciones</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. CCT 130/75 Empleados de Comercio - Categoria Auxiliar Especializado A, sin antiguedad</t>
+          <t xml:space="preserve">  6. Margen bruto sobre PVP: 70% (estimado elab. propia panaderia - validar con costeo recetas)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Sueldo: $1,080,274 remunerativo + $100,000 NR = $1,180,274/empleado (escala Dic 2025 - Mar 2026)</t>
+          <t xml:space="preserve">  7. Comisiones: Credito 3%, Debito 1.2%, Billetera 1.5% (promedios de mercado)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Contribuciones patronales (29.74%) calculadas SOLO sobre remunerativo. NR no genera cargas</t>
+          <t xml:space="preserve">  8. IIBB Mendoza: 3% (Ley Impositiva Mza 2026, Rubro 7 comercio minorista)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. SAC mensualizado sobre base remunerativa + contribuciones</t>
+          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (53.2% ventas). Ley 25.413</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Margen bruto sobre PVP: 70% (estimado elab. propia panaderia - validar con costeo recetas)</t>
+          <t xml:space="preserve">  10. Merma estimada: 4% (pan del dia con vida util corta, tipico 3-5%)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Comisiones: Credito 3%, Debito 1.2%, Billetera 1.5% (promedios de mercado)</t>
+          <t xml:space="preserve">  11. IVA: no se incluye como costo (se compensa DF vs CF). Solo se muestra para referencia</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. IIBB Mendoza: 3% (Ley Impositiva Mza 2026, Rubro 7 comercio minorista)</t>
+          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (53.2% ventas). Ley 25.413</t>
+          <t xml:space="preserve">  13. SOLO incluye PANAD.ELAB.PROPIA (produccion propia). NO incluye reventa (PANIFIC.Y MASAS FRESCAS)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10. Merma estimada: 4% (pan del dia con vida util corta, tipico 3-5%)</t>
+          <t xml:space="preserve">  14. Gas: 1153 m3/mes (hornos industriales ~8-10h/dia). Factura $664,000/1485m3 compartida con rotiseria</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11. IVA: no se incluye como costo (se compensa DF vs CF). Solo se muestra para referencia</t>
+          <t xml:space="preserve">  15. Electricidad: 1100 kWh/mes. Tarifa $365.76/kWh all-in s/factura EDEMSA</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
+          <t xml:space="preserve">  16. Empleados: 3 (confirmado por Sebastian Pena, Mar 2026)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13. Indice estacional ponderado ventana: 0.9432</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  14. SOLO incluye PANAD.ELAB.PROPIA (produccion propia). NO incluye reventa (PANIFIC.Y MASAS FRESCAS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  15. Gas: 1153 m3/mes estimado (hornos industriales ~8-10h/dia). Factura compartida con rotiseria</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  16. Gas: factura Ecogas Patricios 344 $664,000/1485m3. Panad 1153m3 + Rotis 332m3 = 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  17. Electricidad: 1100 kWh/mes estimado (amasadora + sobadora + batidora + fermentadora + camara frio + ilum)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  18. Electricidad tarifa: $365.76/kWh all-in (s/factura EDEMSA Patricios 334 Mar 2026, T2 Especial, IVA 27%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  19. Empleados: 3 (confirmado por Sebastian Peña, Mar 2026)</t>
+          <t xml:space="preserve">  17. NO incluye: alquiler, amortizacion equipos, agua, seguros (excluidos por decision del cliente)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A114:E114"/>
-    <mergeCell ref="A83:E83"/>
+  <mergeCells count="28">
     <mergeCell ref="A98:E98"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
+    <mergeCell ref="A61:E61"/>
     <mergeCell ref="A110:E110"/>
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="A99:E99"/>
+    <mergeCell ref="A89:E89"/>
     <mergeCell ref="A105:E105"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A101:E101"/>
-    <mergeCell ref="A113:E113"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A104:E104"/>
-    <mergeCell ref="A116:E116"/>
     <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
-    <mergeCell ref="A91:E91"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A100:E100"/>
-    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A96:E96"/>
     <mergeCell ref="A102:E102"/>
-    <mergeCell ref="A115:E115"/>
-    <mergeCell ref="A117:E117"/>
-    <mergeCell ref="A93:E93"/>
     <mergeCell ref="A111:E111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2376,13 +2311,13 @@
       <c r="F4" s="6" t="n">
         <v>16943200</v>
       </c>
-      <c r="G4" s="23" t="n">
+      <c r="G4" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>4528778</v>
       </c>
-      <c r="I4" s="23" t="n">
+      <c r="I4" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2407,13 +2342,13 @@
       <c r="F5" s="6" t="n">
         <v>17238765</v>
       </c>
-      <c r="G5" s="23" t="n">
+      <c r="G5" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>4270798</v>
       </c>
-      <c r="I5" s="23" t="n">
+      <c r="I5" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2438,13 +2373,13 @@
       <c r="F6" s="6" t="n">
         <v>21845173</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="32" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>4801257</v>
       </c>
-      <c r="I6" s="23" t="n">
+      <c r="I6" s="32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2875,7 +2810,7 @@
       <c r="G20" s="6" t="n">
         <v>7288811</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
@@ -2906,7 +2841,7 @@
       <c r="G21" s="6" t="n">
         <v>4301065</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H21" s="32" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
@@ -2999,508 +2934,508 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>TORTAS X 6U.</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="34" t="n">
         <v>72992075</v>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="34" t="n">
         <v>56326</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="34" t="n">
         <v>1290</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="34" t="n">
         <v>17.4</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="34" t="n">
         <v>17.4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>PAN NINO FLAUTA</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="34" t="n">
         <v>66961362</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="34" t="n">
         <v>39480</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="34" t="n">
         <v>1872</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="34" t="n">
         <v>33.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>PAN NINO MIÑON</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="34" t="n">
         <v>38748920</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="34" t="n">
         <v>18128</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="34" t="n">
         <v>2173</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="34" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="34" t="n">
         <v>42.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>SACRAMENTO X 6 U</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="34" t="n">
         <v>28464410</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="34" t="n">
         <v>18559</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="34" t="n">
         <v>1528</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="34" t="n">
         <v>6.8</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="34" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>FAC. ESPECIALES X 6U</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="34" t="n">
         <v>26371250</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="34" t="n">
         <v>11937</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="34" t="n">
         <v>2202</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="34" t="n">
         <v>6.3</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="34" t="n">
         <v>55.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>PAN CASERO NINO</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="34" t="n">
         <v>18910362</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="34" t="n">
         <v>6799</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="34" t="n">
         <v>2139</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="34" t="n">
         <v>4.5</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="34" t="n">
         <v>60.3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>PAN SALVADO NINO</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="34" t="n">
         <v>17334776</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="34" t="n">
         <v>2882</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="34" t="n">
         <v>2689</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="34" t="n">
         <v>4.1</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="34" t="n">
         <v>64.5</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>PRE-PIZZA NINO X 2 UNI</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="34" t="n">
         <v>16900885</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="34" t="n">
         <v>7958</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="34" t="n">
         <v>2108</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="34" t="n">
         <v>68.5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>PAN NINO BAGUETTE</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="34" t="n">
         <v>13814098</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="34" t="n">
         <v>1549</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="34" t="n">
         <v>2164</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="34" t="n">
         <v>3.3</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="34" t="n">
         <v>71.8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>TORTAS NINO X 6U.</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="34" t="n">
         <v>13490250</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="34" t="n">
         <v>8149</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="34" t="n">
         <v>1648</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="34" t="n">
         <v>3.2</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="34" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>PAN DULCE NINO CLASICO X 500 GS</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="34" t="n">
         <v>10483830</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="34" t="n">
         <v>2997</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="34" t="n">
         <v>3427</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="34" t="n">
         <v>77.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>BIZCOCHUELO NINO</t>
         </is>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="34" t="n">
         <v>10217573</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="34" t="n">
         <v>1107</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="34" t="n">
         <v>9736</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="34" t="n">
         <v>2.4</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="34" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>PIONONO NINO TRADICIONAL</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="22" t="n">
         <v>9072225</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="22" t="n">
         <v>924</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="22" t="n">
         <v>8320</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="22" t="n">
         <v>2.2</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="22" t="n">
         <v>82.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>NINO DISCOS PARA EMPANADAS  X12U</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B17" s="22" t="n">
         <v>8989610</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="22" t="n">
         <v>7532</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="22" t="n">
         <v>1176</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="22" t="n">
         <v>2.1</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="22" t="n">
         <v>84.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>PAN RALLADO NINO X 500 GRS</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="22" t="n">
         <v>7188920</v>
       </c>
-      <c r="C18" s="18" t="n">
+      <c r="C18" s="22" t="n">
         <v>5194</v>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="22" t="n">
         <v>1376</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="22" t="n">
         <v>1.7</v>
       </c>
-      <c r="F18" s="18" t="n">
+      <c r="F18" s="22" t="n">
         <v>86</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>PIZZETAS NINO X 2 UNI</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n">
+      <c r="B19" s="22" t="n">
         <v>6168210</v>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="22" t="n">
         <v>8538</v>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="22" t="n">
         <v>712</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="F19" s="18" t="n">
+      <c r="F19" s="22" t="n">
         <v>87.5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>PAN DE PANCHOS  NINO  X 6 UN</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n">
+      <c r="B20" s="22" t="n">
         <v>5638610</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="22" t="n">
         <v>4113</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="22" t="n">
         <v>1356</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="22" t="n">
         <v>88.8</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>PRE-PIZZA NINO X 1 UNI</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B21" s="22" t="n">
         <v>5561545</v>
       </c>
-      <c r="C21" s="18" t="n">
+      <c r="C21" s="22" t="n">
         <v>3762</v>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="22" t="n">
         <v>1452</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="22" t="n">
         <v>90.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>PAN HAMBURGUESA X 4 UNI.NINO</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n">
+      <c r="B22" s="22" t="n">
         <v>5318320</v>
       </c>
-      <c r="C22" s="18" t="n">
+      <c r="C22" s="22" t="n">
         <v>3637</v>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="22" t="n">
         <v>1451</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="22" t="n">
         <v>1.3</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="22" t="n">
         <v>91.40000000000001</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>TORTAS X 12U.</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B23" s="22" t="n">
         <v>4629300</v>
       </c>
-      <c r="C23" s="18" t="n">
+      <c r="C23" s="22" t="n">
         <v>1810</v>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="22" t="n">
         <v>2564</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="22" t="n">
         <v>1.1</v>
       </c>
-      <c r="F23" s="18" t="n">
+      <c r="F23" s="22" t="n">
         <v>92.5</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>PAN DE LOMO NINO  X 2 UNID</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n">
+      <c r="B24" s="22" t="n">
         <v>3497015</v>
       </c>
-      <c r="C24" s="18" t="n">
+      <c r="C24" s="22" t="n">
         <v>2146</v>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="22" t="n">
         <v>1620</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="22" t="n">
         <v>0.8</v>
       </c>
-      <c r="F24" s="18" t="n">
+      <c r="F24" s="22" t="n">
         <v>93.40000000000001</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>TORTAS X 1U.</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n">
+      <c r="B25" s="22" t="n">
         <v>2983815</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="22" t="n">
         <v>12198</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="22" t="n">
         <v>243</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="22" t="n">
         <v>0.7</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="22" t="n">
         <v>94.09999999999999</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>PAN DULCE NINO ESP.X500 GR</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n">
+      <c r="B26" s="22" t="n">
         <v>2957284</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="22" t="n">
         <v>513</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="22" t="n">
         <v>5601</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="22" t="n">
         <v>0.7</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="22" t="n">
         <v>94.8</v>
       </c>
     </row>
@@ -3557,7 +3492,7 @@
       <c r="B29" s="6" t="n">
         <v>2262226</v>
       </c>
-      <c r="C29" s="23" t="n">
+      <c r="C29" s="32" t="n">
         <v>67</v>
       </c>
       <c r="D29" s="6" t="n">
@@ -3799,7 +3734,7 @@
       <c r="B40" s="6" t="n">
         <v>442000</v>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="32" t="n">
         <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
@@ -3821,7 +3756,7 @@
       <c r="B41" s="6" t="n">
         <v>399216</v>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C41" s="32" t="n">
         <v>85</v>
       </c>
       <c r="D41" s="6" t="n">
@@ -3843,7 +3778,7 @@
       <c r="B42" s="6" t="n">
         <v>374760</v>
       </c>
-      <c r="C42" s="23" t="n">
+      <c r="C42" s="32" t="n">
         <v>85</v>
       </c>
       <c r="D42" s="6" t="n">
@@ -3887,7 +3822,7 @@
       <c r="B44" s="6" t="n">
         <v>256392</v>
       </c>
-      <c r="C44" s="23" t="n">
+      <c r="C44" s="32" t="n">
         <v>42</v>
       </c>
       <c r="D44" s="6" t="n">
@@ -3909,7 +3844,7 @@
       <c r="B45" s="6" t="n">
         <v>211752</v>
       </c>
-      <c r="C45" s="23" t="n">
+      <c r="C45" s="32" t="n">
         <v>36</v>
       </c>
       <c r="D45" s="6" t="n">
@@ -3931,7 +3866,7 @@
       <c r="B46" s="6" t="n">
         <v>181419</v>
       </c>
-      <c r="C46" s="23" t="n">
+      <c r="C46" s="32" t="n">
         <v>11</v>
       </c>
       <c r="D46" s="6" t="n">
@@ -3953,7 +3888,7 @@
       <c r="B47" s="6" t="n">
         <v>95232</v>
       </c>
-      <c r="C47" s="23" t="n">
+      <c r="C47" s="32" t="n">
         <v>12</v>
       </c>
       <c r="D47" s="6" t="n">
@@ -4019,7 +3954,7 @@
       <c r="B50" s="6" t="n">
         <v>60685</v>
       </c>
-      <c r="C50" s="23" t="n">
+      <c r="C50" s="32" t="n">
         <v>5</v>
       </c>
       <c r="D50" s="6" t="n">
@@ -4063,7 +3998,7 @@
       <c r="B52" s="6" t="n">
         <v>40784</v>
       </c>
-      <c r="C52" s="23" t="n">
+      <c r="C52" s="32" t="n">
         <v>3</v>
       </c>
       <c r="D52" s="6" t="n">
@@ -4085,7 +4020,7 @@
       <c r="B53" s="6" t="n">
         <v>15325</v>
       </c>
-      <c r="C53" s="23" t="n">
+      <c r="C53" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="6" t="n">
@@ -4107,7 +4042,7 @@
       <c r="B54" s="6" t="n">
         <v>11200</v>
       </c>
-      <c r="C54" s="23" t="n">
+      <c r="C54" s="32" t="n">
         <v>7</v>
       </c>
       <c r="D54" s="6" t="n">
@@ -4129,7 +4064,7 @@
       <c r="B55" s="6" t="n">
         <v>9900</v>
       </c>
-      <c r="C55" s="23" t="n">
+      <c r="C55" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="6" t="n">
@@ -4151,7 +4086,7 @@
       <c r="B56" s="6" t="n">
         <v>6900</v>
       </c>
-      <c r="C56" s="23" t="n">
+      <c r="C56" s="32" t="n">
         <v>6</v>
       </c>
       <c r="D56" s="6" t="n">
@@ -4173,7 +4108,7 @@
       <c r="B57" s="6" t="n">
         <v>4200</v>
       </c>
-      <c r="C57" s="23" t="n">
+      <c r="C57" s="32" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="6" t="n">
@@ -4195,7 +4130,7 @@
       <c r="B58" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="C58" s="23" t="n">
+      <c r="C58" s="32" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="6" t="n">
@@ -4214,13 +4149,13 @@
           <t>TORTAS SURTIDAS X 6 UNI.</t>
         </is>
       </c>
-      <c r="B59" s="23" t="n">
+      <c r="B59" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="C59" s="23" t="n">
+      <c r="C59" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="23" t="n">
+      <c r="D59" s="32" t="n">
         <v>0</v>
       </c>
       <c r="E59" s="6" t="n">
@@ -4275,7 +4210,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Precios insumos: sistema POS supermercado NINO x 0.70 (costo mayorista estimado) | Validacion del margen 70%</t>
+          <t>Precios insumos: sistema POS supermercado NINO x 0.70 (costo mayorista estimado)</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4257,7 @@
           <t>Harina 0000 (Florencia)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>1040</v>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -4330,7 +4265,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>728</v>
       </c>
       <c r="E6" s="9" t="inlineStr"/>
@@ -4348,7 +4283,7 @@
           <t>Harina 000 (Florencia)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>750</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4356,7 +4291,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>525</v>
       </c>
       <c r="E7" s="9" t="inlineStr"/>
@@ -4374,7 +4309,7 @@
           <t>Harina integral (Pureza)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>1650</v>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -4382,7 +4317,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="13" t="n">
         <v>1155</v>
       </c>
       <c r="E8" s="9" t="inlineStr"/>
@@ -4400,7 +4335,7 @@
           <t>Manteca (SYS 200g)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <v>11250</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -4408,7 +4343,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="13" t="n">
         <v>7875</v>
       </c>
       <c r="E9" s="9" t="inlineStr"/>
@@ -4426,7 +4361,7 @@
           <t>Grasa vacuna (Swift 1kg)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>4290</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4434,7 +4369,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="13" t="n">
         <v>3003</v>
       </c>
       <c r="E10" s="9" t="inlineStr"/>
@@ -4452,7 +4387,7 @@
           <t>Azucar (Ledesma 1kg)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>1150</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -4460,7 +4395,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="13" t="n">
         <v>805</v>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -4478,7 +4413,7 @@
           <t>Levadura prensada (Virgen)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>11160</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -4486,7 +4421,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="13" t="n">
         <v>7812</v>
       </c>
       <c r="E12" s="9" t="inlineStr"/>
@@ -4504,7 +4439,7 @@
           <t>Huevos x6</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>1750</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -4512,7 +4447,7 @@
           <t>$/6u</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>1225</v>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -4530,7 +4465,7 @@
           <t>Huevos maple 30u</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="13" t="n">
         <v>7400</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -4538,7 +4473,7 @@
           <t>$/30u</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="13" t="n">
         <v>5180</v>
       </c>
       <c r="E14" s="9" t="inlineStr"/>
@@ -4556,7 +4491,7 @@
           <t>Sal fina (Dos Anclas 500g)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="13" t="n">
         <v>2200</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -4564,7 +4499,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="13" t="n">
         <v>1540</v>
       </c>
       <c r="E15" s="9" t="inlineStr"/>
@@ -4582,7 +4517,7 @@
           <t>Dulce de leche (Sta Maria 1kg)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="13" t="n">
         <v>5000</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -4590,7 +4525,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="13" t="n">
         <v>3500</v>
       </c>
       <c r="E16" s="9" t="inlineStr"/>
@@ -4608,7 +4543,7 @@
           <t>Dulce de membrillo (D. Francisco)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <v>3590</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -4616,7 +4551,7 @@
           <t>$/kg</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="13" t="n">
         <v>2513</v>
       </c>
       <c r="E17" s="9" t="inlineStr"/>
@@ -4634,7 +4569,7 @@
           <t>Aceite girasol (Natura 900ml)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="13" t="n">
         <v>4111</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -4642,7 +4577,7 @@
           <t>$/L</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="13" t="n">
         <v>2878</v>
       </c>
       <c r="E18" s="9" t="inlineStr"/>
@@ -4660,7 +4595,7 @@
           <t>Leche sachet (Serenisima 1L)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -4668,7 +4603,7 @@
           <t>$/L</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="13" t="n">
         <v>1050</v>
       </c>
       <c r="E19" s="9" t="inlineStr"/>
@@ -4730,20 +4665,20 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>TORTAS NINO x6 (facturas)</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr"/>
-      <c r="C23" s="26" t="inlineStr"/>
-      <c r="D23" s="26" t="inlineStr"/>
-      <c r="E23" s="26" t="inlineStr"/>
-      <c r="F23" s="27" t="n">
+      <c r="B23" s="35" t="inlineStr"/>
+      <c r="C23" s="35" t="inlineStr"/>
+      <c r="D23" s="35" t="inlineStr"/>
+      <c r="E23" s="35" t="inlineStr"/>
+      <c r="F23" s="36" t="n">
         <v>1663</v>
       </c>
-      <c r="G23" s="26" t="inlineStr"/>
-      <c r="H23" s="26" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr"/>
+      <c r="H23" s="35" t="inlineStr">
         <is>
           <t>20.9%</t>
         </is>
@@ -4755,7 +4690,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -4763,10 +4698,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="13" t="n">
         <v>208</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="13" t="n">
         <v>146</v>
       </c>
       <c r="F24" s="9" t="inlineStr"/>
@@ -4779,7 +4714,7 @@
           <t xml:space="preserve">  Grasa vacuna</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -4787,10 +4722,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>429</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>300</v>
       </c>
       <c r="F25" s="9" t="inlineStr"/>
@@ -4803,7 +4738,7 @@
           <t xml:space="preserve">  Azucar</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="13" t="n">
         <v>0.03</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -4811,10 +4746,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>34</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>24</v>
       </c>
       <c r="F26" s="9" t="inlineStr"/>
@@ -4827,7 +4762,7 @@
           <t xml:space="preserve">  Levadura prensada</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="13" t="n">
         <v>0.01</v>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -4835,10 +4770,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>78</v>
       </c>
       <c r="F27" s="9" t="inlineStr"/>
@@ -4851,7 +4786,7 @@
           <t xml:space="preserve">  Huevo (1/2)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -4859,10 +4794,10 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="13" t="n">
         <v>146</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="13" t="n">
         <v>102</v>
       </c>
       <c r="F28" s="9" t="inlineStr"/>
@@ -4875,7 +4810,7 @@
           <t xml:space="preserve">  Sal/esencia</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n">
+      <c r="B29" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -4883,10 +4818,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>35</v>
       </c>
       <c r="F29" s="9" t="inlineStr"/>
@@ -4916,20 +4851,20 @@
       <c r="H30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>PAN NINO FLAUTA (u)</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr"/>
-      <c r="C31" s="26" t="inlineStr"/>
-      <c r="D31" s="26" t="inlineStr"/>
-      <c r="E31" s="26" t="inlineStr"/>
-      <c r="F31" s="27" t="n">
+      <c r="B31" s="35" t="inlineStr"/>
+      <c r="C31" s="35" t="inlineStr"/>
+      <c r="D31" s="35" t="inlineStr"/>
+      <c r="E31" s="35" t="inlineStr"/>
+      <c r="F31" s="36" t="n">
         <v>2200</v>
       </c>
-      <c r="G31" s="26" t="inlineStr"/>
-      <c r="H31" s="26" t="inlineStr">
+      <c r="G31" s="35" t="inlineStr"/>
+      <c r="H31" s="35" t="inlineStr">
         <is>
           <t>16.9%</t>
         </is>
@@ -4941,7 +4876,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -4949,10 +4884,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="13" t="n">
         <v>312</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="13" t="n">
         <v>218</v>
       </c>
       <c r="F32" s="9" t="inlineStr"/>
@@ -4965,7 +4900,7 @@
           <t xml:space="preserve">  Sal fina</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>0.005</v>
       </c>
       <c r="C33" s="9" t="inlineStr">
@@ -4973,10 +4908,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>8</v>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -4989,7 +4924,7 @@
           <t xml:space="preserve">  Levadura prensada</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="13" t="n">
         <v>0.005</v>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -4997,10 +4932,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>39</v>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -5013,7 +4948,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -5021,10 +4956,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -5054,20 +4989,20 @@
       <c r="H36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>PAN NINO MIÑON (u)</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr"/>
-      <c r="C37" s="26" t="inlineStr"/>
-      <c r="D37" s="26" t="inlineStr"/>
-      <c r="E37" s="26" t="inlineStr"/>
-      <c r="F37" s="27" t="n">
+      <c r="A37" s="35" t="inlineStr">
+        <is>
+          <t>PAN NINO MINON (u)</t>
+        </is>
+      </c>
+      <c r="B37" s="35" t="inlineStr"/>
+      <c r="C37" s="35" t="inlineStr"/>
+      <c r="D37" s="35" t="inlineStr"/>
+      <c r="E37" s="35" t="inlineStr"/>
+      <c r="F37" s="36" t="n">
         <v>2501</v>
       </c>
-      <c r="G37" s="26" t="inlineStr"/>
-      <c r="H37" s="26" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr"/>
+      <c r="H37" s="35" t="inlineStr">
         <is>
           <t>9.2%</t>
         </is>
@@ -5079,7 +5014,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="C38" s="9" t="inlineStr">
@@ -5087,10 +5022,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="13" t="n">
         <v>260</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>182</v>
       </c>
       <c r="F38" s="9" t="inlineStr"/>
@@ -5103,7 +5038,7 @@
           <t xml:space="preserve">  Grasa vacuna</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="13" t="n">
         <v>0.03</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
@@ -5111,10 +5046,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="13" t="n">
         <v>129</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>90</v>
       </c>
       <c r="F39" s="9" t="inlineStr"/>
@@ -5127,7 +5062,7 @@
           <t xml:space="preserve">  Sal/levadura</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
+      <c r="B40" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -5135,10 +5070,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>56</v>
       </c>
       <c r="F40" s="9" t="inlineStr"/>
@@ -5151,7 +5086,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -5159,10 +5094,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="9" t="inlineStr"/>
@@ -5192,20 +5127,20 @@
       <c r="H42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>SACRAMENTO x6 (facturas)</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr"/>
-      <c r="C43" s="26" t="inlineStr"/>
-      <c r="D43" s="26" t="inlineStr"/>
-      <c r="E43" s="26" t="inlineStr"/>
-      <c r="F43" s="27" t="n">
+      <c r="B43" s="35" t="inlineStr"/>
+      <c r="C43" s="35" t="inlineStr"/>
+      <c r="D43" s="35" t="inlineStr"/>
+      <c r="E43" s="35" t="inlineStr"/>
+      <c r="F43" s="36" t="n">
         <v>1760</v>
       </c>
-      <c r="G43" s="26" t="inlineStr"/>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="G43" s="35" t="inlineStr"/>
+      <c r="H43" s="35" t="inlineStr">
         <is>
           <t>7.0%</t>
         </is>
@@ -5217,7 +5152,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C44" s="9" t="inlineStr">
@@ -5225,10 +5160,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D44" s="13" t="n">
         <v>208</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="13" t="n">
         <v>146</v>
       </c>
       <c r="F44" s="9" t="inlineStr"/>
@@ -5241,7 +5176,7 @@
           <t xml:space="preserve">  Grasa vacuna</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="13" t="n">
         <v>0.08</v>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -5249,10 +5184,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D45" s="13" t="n">
         <v>343</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="E45" s="13" t="n">
         <v>240</v>
       </c>
       <c r="F45" s="9" t="inlineStr"/>
@@ -5265,7 +5200,7 @@
           <t xml:space="preserve">  Azucar</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="13" t="n">
         <v>0.04</v>
       </c>
       <c r="C46" s="9" t="inlineStr">
@@ -5273,10 +5208,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="14" t="n">
         <v>32</v>
       </c>
       <c r="F46" s="9" t="inlineStr"/>
@@ -5289,7 +5224,7 @@
           <t xml:space="preserve">  Dulce de membrillo</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="13" t="n">
         <v>0.06</v>
       </c>
       <c r="C47" s="9" t="inlineStr">
@@ -5297,10 +5232,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D47" s="13" t="n">
         <v>215</v>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="13" t="n">
         <v>151</v>
       </c>
       <c r="F47" s="9" t="inlineStr"/>
@@ -5313,7 +5248,7 @@
           <t xml:space="preserve">  Levadura/sal</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -5321,10 +5256,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <v>56</v>
       </c>
       <c r="F48" s="9" t="inlineStr"/>
@@ -5354,20 +5289,20 @@
       <c r="H49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>FAC. ESPECIALES x6</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr"/>
-      <c r="C50" s="26" t="inlineStr"/>
-      <c r="D50" s="26" t="inlineStr"/>
-      <c r="E50" s="26" t="inlineStr"/>
-      <c r="F50" s="27" t="n">
+      <c r="B50" s="35" t="inlineStr"/>
+      <c r="C50" s="35" t="inlineStr"/>
+      <c r="D50" s="35" t="inlineStr"/>
+      <c r="E50" s="35" t="inlineStr"/>
+      <c r="F50" s="36" t="n">
         <v>2511</v>
       </c>
-      <c r="G50" s="26" t="inlineStr"/>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="G50" s="35" t="inlineStr"/>
+      <c r="H50" s="35" t="inlineStr">
         <is>
           <t>6.4%</t>
         </is>
@@ -5379,7 +5314,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="13" t="n">
         <v>0.22</v>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -5387,10 +5322,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="13" t="n">
         <v>229</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="E51" s="13" t="n">
         <v>160</v>
       </c>
       <c r="F51" s="9" t="inlineStr"/>
@@ -5403,7 +5338,7 @@
           <t xml:space="preserve">  Manteca</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="13" t="n">
         <v>0.08</v>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -5411,10 +5346,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="D52" s="13" t="n">
         <v>900</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="E52" s="13" t="n">
         <v>630</v>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -5427,7 +5362,7 @@
           <t xml:space="preserve">  Azucar</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>0.04</v>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -5435,10 +5370,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="14" t="n">
         <v>32</v>
       </c>
       <c r="F53" s="9" t="inlineStr"/>
@@ -5451,7 +5386,7 @@
           <t xml:space="preserve">  Dulce de leche</t>
         </is>
       </c>
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="13" t="n">
         <v>0.04</v>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -5459,10 +5394,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D54" s="12" t="n">
+      <c r="D54" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="13" t="n">
         <v>140</v>
       </c>
       <c r="F54" s="9" t="inlineStr"/>
@@ -5475,7 +5410,7 @@
           <t xml:space="preserve">  Levadura/huevo</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n">
+      <c r="B55" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -5483,10 +5418,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="D55" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="13" t="n">
         <v>140</v>
       </c>
       <c r="F55" s="9" t="inlineStr"/>
@@ -5516,20 +5451,20 @@
       <c r="H56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>PAN SALVADO NINO (u)</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr"/>
-      <c r="C57" s="26" t="inlineStr"/>
-      <c r="D57" s="26" t="inlineStr"/>
-      <c r="E57" s="26" t="inlineStr"/>
-      <c r="F57" s="27" t="n">
+      <c r="B57" s="35" t="inlineStr"/>
+      <c r="C57" s="35" t="inlineStr"/>
+      <c r="D57" s="35" t="inlineStr"/>
+      <c r="E57" s="35" t="inlineStr"/>
+      <c r="F57" s="36" t="n">
         <v>3498</v>
       </c>
-      <c r="G57" s="26" t="inlineStr"/>
-      <c r="H57" s="26" t="inlineStr">
+      <c r="G57" s="35" t="inlineStr"/>
+      <c r="H57" s="35" t="inlineStr">
         <is>
           <t>5.2%</t>
         </is>
@@ -5541,7 +5476,7 @@
           <t xml:space="preserve">  Harina integral</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n">
+      <c r="B58" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
@@ -5549,10 +5484,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D58" s="12" t="n">
+      <c r="D58" s="13" t="n">
         <v>495</v>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="E58" s="13" t="n">
         <v>346</v>
       </c>
       <c r="F58" s="9" t="inlineStr"/>
@@ -5565,7 +5500,7 @@
           <t xml:space="preserve">  Salvado trigo</t>
         </is>
       </c>
-      <c r="B59" s="12" t="n">
+      <c r="B59" s="13" t="n">
         <v>0.05</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -5573,10 +5508,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="14" t="n">
         <v>28</v>
       </c>
       <c r="F59" s="9" t="inlineStr"/>
@@ -5589,7 +5524,7 @@
           <t xml:space="preserve">  Sal/levadura</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
@@ -5597,10 +5532,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="14" t="n">
         <v>56</v>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -5613,7 +5548,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -5621,10 +5556,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="9" t="inlineStr"/>
@@ -5654,20 +5589,20 @@
       <c r="H62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>PAN CASERO NINO (u)</t>
         </is>
       </c>
-      <c r="B63" s="26" t="inlineStr"/>
-      <c r="C63" s="26" t="inlineStr"/>
-      <c r="D63" s="26" t="inlineStr"/>
-      <c r="E63" s="26" t="inlineStr"/>
-      <c r="F63" s="27" t="n">
+      <c r="B63" s="35" t="inlineStr"/>
+      <c r="C63" s="35" t="inlineStr"/>
+      <c r="D63" s="35" t="inlineStr"/>
+      <c r="E63" s="35" t="inlineStr"/>
+      <c r="F63" s="36" t="n">
         <v>2501</v>
       </c>
-      <c r="G63" s="26" t="inlineStr"/>
-      <c r="H63" s="26" t="inlineStr">
+      <c r="G63" s="35" t="inlineStr"/>
+      <c r="H63" s="35" t="inlineStr">
         <is>
           <t>4.8%</t>
         </is>
@@ -5679,7 +5614,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -5687,10 +5622,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D64" s="12" t="n">
+      <c r="D64" s="13" t="n">
         <v>312</v>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="E64" s="13" t="n">
         <v>218</v>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -5703,7 +5638,7 @@
           <t xml:space="preserve">  Grasa vacuna</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="13" t="n">
         <v>0.03</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -5711,10 +5646,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D65" s="12" t="n">
+      <c r="D65" s="13" t="n">
         <v>129</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="14" t="n">
         <v>90</v>
       </c>
       <c r="F65" s="9" t="inlineStr"/>
@@ -5727,7 +5662,7 @@
           <t xml:space="preserve">  Sal/levadura</t>
         </is>
       </c>
-      <c r="B66" s="13" t="n">
+      <c r="B66" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -5735,10 +5670,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="14" t="n">
         <v>56</v>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -5751,7 +5686,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n">
+      <c r="B67" s="13" t="n">
         <v>0.15</v>
       </c>
       <c r="C67" s="9" t="inlineStr">
@@ -5759,10 +5694,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="9" t="inlineStr"/>
@@ -5792,20 +5727,20 @@
       <c r="H68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>PRE-PIZZA NINO x2</t>
         </is>
       </c>
-      <c r="B69" s="26" t="inlineStr"/>
-      <c r="C69" s="26" t="inlineStr"/>
-      <c r="D69" s="26" t="inlineStr"/>
-      <c r="E69" s="26" t="inlineStr"/>
-      <c r="F69" s="27" t="n">
+      <c r="B69" s="35" t="inlineStr"/>
+      <c r="C69" s="35" t="inlineStr"/>
+      <c r="D69" s="35" t="inlineStr"/>
+      <c r="E69" s="35" t="inlineStr"/>
+      <c r="F69" s="36" t="n">
         <v>2871</v>
       </c>
-      <c r="G69" s="26" t="inlineStr"/>
-      <c r="H69" s="26" t="inlineStr">
+      <c r="G69" s="35" t="inlineStr"/>
+      <c r="H69" s="35" t="inlineStr">
         <is>
           <t>4.3%</t>
         </is>
@@ -5817,7 +5752,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B70" s="13" t="n">
         <v>0.4</v>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -5825,10 +5760,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D70" s="12" t="n">
+      <c r="D70" s="13" t="n">
         <v>416</v>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="E70" s="13" t="n">
         <v>291</v>
       </c>
       <c r="F70" s="9" t="inlineStr"/>
@@ -5841,7 +5776,7 @@
           <t xml:space="preserve">  Aceite girasol</t>
         </is>
       </c>
-      <c r="B71" s="12" t="n">
+      <c r="B71" s="13" t="n">
         <v>0.05</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5849,10 +5784,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D71" s="12" t="n">
+      <c r="D71" s="13" t="n">
         <v>206</v>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="E71" s="13" t="n">
         <v>144</v>
       </c>
       <c r="F71" s="9" t="inlineStr"/>
@@ -5865,7 +5800,7 @@
           <t xml:space="preserve">  Sal/levadura</t>
         </is>
       </c>
-      <c r="B72" s="13" t="n">
+      <c r="B72" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5873,10 +5808,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="14" t="n">
         <v>56</v>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -5889,7 +5824,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5897,10 +5832,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="9" t="inlineStr"/>
@@ -5930,20 +5865,20 @@
       <c r="H74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>PAN NINO BAGUETTE (u)</t>
         </is>
       </c>
-      <c r="B75" s="26" t="inlineStr"/>
-      <c r="C75" s="26" t="inlineStr"/>
-      <c r="D75" s="26" t="inlineStr"/>
-      <c r="E75" s="26" t="inlineStr"/>
-      <c r="F75" s="27" t="n">
+      <c r="B75" s="35" t="inlineStr"/>
+      <c r="C75" s="35" t="inlineStr"/>
+      <c r="D75" s="35" t="inlineStr"/>
+      <c r="E75" s="35" t="inlineStr"/>
+      <c r="F75" s="36" t="n">
         <v>2492</v>
       </c>
-      <c r="G75" s="26" t="inlineStr"/>
-      <c r="H75" s="26" t="inlineStr">
+      <c r="G75" s="35" t="inlineStr"/>
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>3.5%</t>
         </is>
@@ -5955,7 +5890,7 @@
           <t xml:space="preserve">  Harina 000</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B76" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5963,10 +5898,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D76" s="12" t="n">
+      <c r="D76" s="13" t="n">
         <v>262</v>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="E76" s="13" t="n">
         <v>184</v>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -5979,7 +5914,7 @@
           <t xml:space="preserve">  Sal fina</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n">
+      <c r="B77" s="13" t="n">
         <v>0.006</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5987,10 +5922,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D77" s="13" t="n">
+      <c r="D77" s="14" t="n">
         <v>13</v>
       </c>
-      <c r="E77" s="13" t="n">
+      <c r="E77" s="14" t="n">
         <v>9</v>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -6003,7 +5938,7 @@
           <t xml:space="preserve">  Levadura prensada</t>
         </is>
       </c>
-      <c r="B78" s="12" t="n">
+      <c r="B78" s="13" t="n">
         <v>0.005</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -6011,10 +5946,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D78" s="13" t="n">
+      <c r="D78" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="E78" s="13" t="n">
+      <c r="E78" s="14" t="n">
         <v>39</v>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -6027,7 +5962,7 @@
           <t xml:space="preserve">  Agua</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n">
+      <c r="B79" s="13" t="n">
         <v>0.22</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -6035,10 +5970,10 @@
           <t>L</t>
         </is>
       </c>
-      <c r="D79" s="13" t="n">
+      <c r="D79" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="13" t="n">
+      <c r="E79" s="14" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="9" t="inlineStr"/>
@@ -6068,20 +6003,20 @@
       <c r="H80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="35" t="inlineStr">
         <is>
           <t>BIZCOCHUELO NINO (u)</t>
         </is>
       </c>
-      <c r="B81" s="26" t="inlineStr"/>
-      <c r="C81" s="26" t="inlineStr"/>
-      <c r="D81" s="26" t="inlineStr"/>
-      <c r="E81" s="26" t="inlineStr"/>
-      <c r="F81" s="27" t="n">
+      <c r="B81" s="35" t="inlineStr"/>
+      <c r="C81" s="35" t="inlineStr"/>
+      <c r="D81" s="35" t="inlineStr"/>
+      <c r="E81" s="35" t="inlineStr"/>
+      <c r="F81" s="36" t="n">
         <v>11731</v>
       </c>
-      <c r="G81" s="26" t="inlineStr"/>
-      <c r="H81" s="26" t="inlineStr">
+      <c r="G81" s="35" t="inlineStr"/>
+      <c r="H81" s="35" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
@@ -6093,7 +6028,7 @@
           <t xml:space="preserve">  Harina 0000</t>
         </is>
       </c>
-      <c r="B82" s="12" t="n">
+      <c r="B82" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6101,10 +6036,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D82" s="12" t="n">
+      <c r="D82" s="13" t="n">
         <v>312</v>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="E82" s="13" t="n">
         <v>218</v>
       </c>
       <c r="F82" s="9" t="inlineStr"/>
@@ -6117,7 +6052,7 @@
           <t xml:space="preserve">  Huevos</t>
         </is>
       </c>
-      <c r="B83" s="13" t="n">
+      <c r="B83" s="14" t="n">
         <v>6</v>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -6125,10 +6060,10 @@
           <t>u</t>
         </is>
       </c>
-      <c r="D83" s="12" t="n">
+      <c r="D83" s="13" t="n">
         <v>1752</v>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="E83" s="13" t="n">
         <v>1226</v>
       </c>
       <c r="F83" s="9" t="inlineStr"/>
@@ -6141,7 +6076,7 @@
           <t xml:space="preserve">  Azucar</t>
         </is>
       </c>
-      <c r="B84" s="12" t="n">
+      <c r="B84" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -6149,10 +6084,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D84" s="12" t="n">
+      <c r="D84" s="13" t="n">
         <v>288</v>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E84" s="13" t="n">
         <v>201</v>
       </c>
       <c r="F84" s="9" t="inlineStr"/>
@@ -6165,7 +6100,7 @@
           <t xml:space="preserve">  Manteca</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n">
+      <c r="B85" s="13" t="n">
         <v>0.05</v>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -6173,10 +6108,10 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D85" s="12" t="n">
+      <c r="D85" s="13" t="n">
         <v>562</v>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="E85" s="13" t="n">
         <v>394</v>
       </c>
       <c r="F85" s="9" t="inlineStr"/>
@@ -6189,7 +6124,7 @@
           <t xml:space="preserve">  Esencia vainilla</t>
         </is>
       </c>
-      <c r="B86" s="13" t="n">
+      <c r="B86" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C86" s="9" t="inlineStr">
@@ -6197,10 +6132,10 @@
           <t>lote</t>
         </is>
       </c>
-      <c r="D86" s="12" t="n">
+      <c r="D86" s="13" t="n">
         <v>100</v>
       </c>
-      <c r="E86" s="13" t="n">
+      <c r="E86" s="14" t="n">
         <v>70</v>
       </c>
       <c r="F86" s="9" t="inlineStr"/>
@@ -6248,27 +6183,27 @@
       <c r="H89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="19" t="inlineStr">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>Margen asumido en estructura de costos</t>
         </is>
       </c>
-      <c r="B90" s="19" t="inlineStr"/>
-      <c r="C90" s="19" t="inlineStr"/>
-      <c r="D90" s="19" t="inlineStr"/>
-      <c r="E90" s="19" t="inlineStr"/>
-      <c r="F90" s="19" t="inlineStr"/>
-      <c r="G90" s="19" t="inlineStr">
+      <c r="B90" s="25" t="inlineStr"/>
+      <c r="C90" s="25" t="inlineStr"/>
+      <c r="D90" s="25" t="inlineStr"/>
+      <c r="E90" s="25" t="inlineStr"/>
+      <c r="F90" s="25" t="inlineStr"/>
+      <c r="G90" s="25" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="H90" s="19" t="inlineStr"/>
+      <c r="H90" s="25" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Factor costo 0.70 = precio retail del super x 70% (margen tipico supermercado ~30%). Ajustar si se conoce el costo real.</t>
+          <t xml:space="preserve">  Factor costo 0.70 = precio retail x 70% (margen tipico supermercado ~30%)</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6217,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOTA: El margen de panaderia propia es alto porque los insumos (harina, agua, sal) son baratos. El costo real es la mano de obra + energia.</t>
+          <t xml:space="preserve">  NOTA: Margen alto porque insumos (harina, agua, sal) son baratos. El costo real es mano de obra + energia.</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6260,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>Escenarios variando Margen Bruto y Merma:</t>
         </is>
@@ -6364,157 +6299,157 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>Pesimista</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>6536850</v>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>22.3%</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="D6" s="34" t="n">
+        <v>7051850</v>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>SUPERAVIT</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>9179107</v>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>31.3%</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="D7" s="34" t="n">
+        <v>9694107</v>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>33.0%</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>SUPERAVIT</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>11527779</v>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>39.3%</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="D8" s="34" t="n">
+        <v>12042779</v>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>SUPERAVIT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>13289283</v>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>45.3%</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="D9" s="34" t="n">
+        <v>13804283</v>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>47.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>SUPERAVIT</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>15050787</v>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
-        <is>
-          <t>51.3%</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
+      <c r="D10" s="34" t="n">
+        <v>15565787</v>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>53.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>SUPERAVIT</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Punto de equilibrio por escenario:</t>
         </is>
@@ -6553,150 +6488,150 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>Pesimista</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
-        <v>14642696</v>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>200%</t>
-        </is>
-      </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="D15" s="34" t="n">
+        <v>13483332</v>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>218%</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>63%</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>12175792</v>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>241%</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
+      <c r="D16" s="34" t="n">
+        <v>11211750</v>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>262%</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
-        <v>10589909</v>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>277%</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="D17" s="34" t="n">
+        <v>9751433</v>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>301%</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
-        <v>9647480</v>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>304%</t>
-        </is>
-      </c>
-      <c r="F18" s="24" t="inlineStr">
+      <c r="D18" s="34" t="n">
+        <v>8883622</v>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>330%</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>Ideal</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
-        <v>8859082</v>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
-        <is>
-          <t>331%</t>
-        </is>
-      </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="D19" s="34" t="n">
+        <v>8157647</v>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>360%</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6705,12 +6640,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOTA: Si la empresa obtiene certificado MiPyME, las contribuciones bajan de 20.4% a 18% SUSS, mejorando todos los escenarios.</t>
+          <t xml:space="preserve">  NOTA: Si obtiene certificado MiPyME, contribuciones SUSS bajan de 20.74% a ~18%, mejorando todos los escenarios.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Comparacion Panaderia vs Rotiseria:</t>
         </is>
@@ -6788,13 +6723,13 @@
           <t>Empleados</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n">
+      <c r="B28" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="23" t="n">
+      <c r="C28" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="32" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
@@ -6810,13 +6745,17 @@
         <v>-4856529</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-4844593</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>-11936</v>
+        <v>-4856529</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Misma dotacion y CCT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/nino/PANADERIA/Estructura_Costos_Panaderia_NINO.xlsx
+++ b/nino/PANADERIA/Estructura_Costos_Panaderia_NINO.xlsx
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base: ultimos 31 dias (16/02/2026 - 18/03/2026) desestacionalizado | Elaborado: Marzo 2026</t>
+          <t>Base: ultimos 31 dias (01/03/2026 - 31/03/2026) desestacionalizado | Elaborado: Marzo 2026</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>29358404</v>
+        <v>21742317</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tickets promedio/mes: 9,905 | Ticket prom: $2,964</t>
+          <t xml:space="preserve">  Tickets promedio/mes: 9,621 | Ticket prom: $2,260</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr"/>
@@ -731,7 +731,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Efectivo 46.8% | Debito 24.0% | Credito 14.3% | Billetera 14.9%</t>
+          <t xml:space="preserve">  Efectivo 45.4% | Debito 23.4% | Credito 13.9% | Billetera 14.5%</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr"/>
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>-3272484</v>
+        <v>-2354078</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -830,11 +830,11 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>-4291445</v>
+        <v>-3204715</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>-602637</v>
+        <v>-453934</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>-406024</v>
+        <v>-305946</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -905,11 +905,11 @@
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>-189365</v>
+        <v>-145480</v>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>-45566</v>
+        <v>-58543</v>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
@@ -1638,11 +1638,11 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Tarjeta Credito (14.3% ventas)</t>
+          <t>Tarjeta Credito (13.9% ventas)</t>
         </is>
       </c>
       <c r="B64" s="6">
-        <f>-B8*0.142708*0.03</f>
+        <f>-B8*0.138617*0.03</f>
         <v/>
       </c>
       <c r="C64" s="24">
@@ -1663,11 +1663,11 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Tarjeta Debito (24.0% ventas)</t>
+          <t>Tarjeta Debito (23.4% ventas)</t>
         </is>
       </c>
       <c r="B65" s="6">
-        <f>-B8*0.240486*0.012</f>
+        <f>-B8*0.233593*0.012</f>
         <v/>
       </c>
       <c r="C65" s="24">
@@ -1688,11 +1688,11 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Billetera Virtual (14.9% ventas)</t>
+          <t>Billetera Virtual (14.5% ventas)</t>
         </is>
       </c>
       <c r="B66" s="6">
-        <f>-B8*0.149097*0.015</f>
+        <f>-B8*0.144823*0.015</f>
         <v/>
       </c>
       <c r="C66" s="24">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="B71" s="6">
-        <f>-B8*0.532291*0.012</f>
+        <f>-B8*0.545697*0.012</f>
         <v/>
       </c>
       <c r="C71" s="24">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Ley 25.413. Solo s/bancarizado (53.2% ventas, excluye efectivo)</t>
+          <t>Ley 25.413. Solo s/bancarizado (54.6% ventas, excluye efectivo)</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (53.2% ventas). Ley 25.413</t>
+          <t xml:space="preserve">  9. Imp. Debitos/Creditos: 1.2% SOLO sobre bancarizado (54.6% ventas). Ley 25.413</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (16/02/2026 - 18/03/2026) desestacionalizados con indice 2025</t>
+          <t xml:space="preserve">  12. Ventas: ultimos 31 dias reales (01/03/2026 - 31/03/2026) desestacionalizados con indice 2025</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>16157314</v>
+        <v>24413440</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>5757</v>
+        <v>9334</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>8606</v>
+        <v>12209</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>2807</v>
+        <v>2616</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>8161351</v>
@@ -2848,26 +2848,57 @@
         <v>3694898</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>4091463</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1490</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1628</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2746</v>
+      </c>
+      <c r="F22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>418436114</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>166906</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>253225</v>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="n">
+        <v>430783703</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>171973</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>258457</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2883,7 +2914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2949,10 +2980,10 @@
         <v>1290</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="5">
@@ -2962,19 +2993,19 @@
         </is>
       </c>
       <c r="B5" s="34" t="n">
-        <v>66961362</v>
+        <v>69966826</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>39480</v>
+        <v>40846</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>1872</v>
+        <v>1884</v>
       </c>
       <c r="E5" s="34" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="F5" s="34" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="6">
@@ -2984,19 +3015,19 @@
         </is>
       </c>
       <c r="B6" s="34" t="n">
-        <v>38748920</v>
+        <v>40366595</v>
       </c>
       <c r="C6" s="34" t="n">
-        <v>18128</v>
+        <v>18775</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>2173</v>
+        <v>2184</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="7">
@@ -3015,10 +3046,10 @@
         <v>1528</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="8">
@@ -3037,10 +3068,10 @@
         <v>2202</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>55.8</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="9">
@@ -3050,19 +3081,19 @@
         </is>
       </c>
       <c r="B9" s="34" t="n">
-        <v>18910362</v>
+        <v>19670562</v>
       </c>
       <c r="C9" s="34" t="n">
-        <v>6799</v>
+        <v>7103</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>2139</v>
+        <v>2150</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>60.3</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="10">
@@ -3072,19 +3103,19 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>17334776</v>
+        <v>18097846</v>
       </c>
       <c r="C10" s="34" t="n">
-        <v>2882</v>
+        <v>3100</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>2689</v>
+        <v>2715</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>64.5</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -3094,19 +3125,19 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>16900885</v>
+        <v>17700565</v>
       </c>
       <c r="C11" s="34" t="n">
-        <v>7958</v>
+        <v>8230</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>2108</v>
+        <v>2133</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>68.5</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="12">
@@ -3116,19 +3147,19 @@
         </is>
       </c>
       <c r="B12" s="34" t="n">
-        <v>13814098</v>
+        <v>14387648</v>
       </c>
       <c r="C12" s="34" t="n">
-        <v>1549</v>
+        <v>1778</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>2164</v>
+        <v>2175</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>3.3</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="13">
@@ -3147,98 +3178,98 @@
         <v>1648</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>75</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>PAN DULCE NINO CLASICO X 500 GS</t>
+          <t>BIZCOCHUELO NINO</t>
         </is>
       </c>
       <c r="B14" s="34" t="n">
-        <v>10483830</v>
+        <v>10824072</v>
       </c>
       <c r="C14" s="34" t="n">
-        <v>2997</v>
+        <v>1160</v>
       </c>
       <c r="D14" s="34" t="n">
-        <v>3427</v>
+        <v>9804</v>
       </c>
       <c r="E14" s="34" t="n">
         <v>2.5</v>
       </c>
       <c r="F14" s="34" t="n">
-        <v>77.5</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="33" t="inlineStr">
         <is>
-          <t>BIZCOCHUELO NINO</t>
+          <t>PAN DULCE NINO CLASICO X 500 GS</t>
         </is>
       </c>
       <c r="B15" s="34" t="n">
-        <v>10217573</v>
+        <v>10483830</v>
       </c>
       <c r="C15" s="34" t="n">
-        <v>1107</v>
+        <v>2997</v>
       </c>
       <c r="D15" s="34" t="n">
-        <v>9736</v>
+        <v>3424</v>
       </c>
       <c r="E15" s="34" t="n">
         <v>2.4</v>
       </c>
       <c r="F15" s="34" t="n">
-        <v>80</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>PIONONO NINO TRADICIONAL</t>
+          <t>NINO DISCOS PARA EMPANADAS  X12U</t>
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>9072225</v>
+        <v>9601130</v>
       </c>
       <c r="C16" s="22" t="n">
-        <v>924</v>
+        <v>7948</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>8320</v>
+        <v>1187</v>
       </c>
       <c r="E16" s="22" t="n">
         <v>2.2</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>82.2</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="inlineStr">
         <is>
-          <t>NINO DISCOS PARA EMPANADAS  X12U</t>
+          <t>PIONONO NINO TRADICIONAL</t>
         </is>
       </c>
       <c r="B17" s="22" t="n">
-        <v>8989610</v>
+        <v>9381749</v>
       </c>
       <c r="C17" s="22" t="n">
-        <v>7532</v>
+        <v>955</v>
       </c>
       <c r="D17" s="22" t="n">
-        <v>1176</v>
+        <v>8362</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -3248,19 +3279,19 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>7188920</v>
+        <v>7481290</v>
       </c>
       <c r="C18" s="22" t="n">
-        <v>5194</v>
+        <v>5367</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="E18" s="22" t="n">
         <v>1.7</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>86</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="19">
@@ -3270,63 +3301,63 @@
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>6168210</v>
+        <v>6471210</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>8538</v>
+        <v>8841</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="E19" s="22" t="n">
         <v>1.5</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>87.5</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>PAN DE PANCHOS  NINO  X 6 UN</t>
+          <t>PRE-PIZZA NINO X 1 UNI</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>5638610</v>
+        <v>5807780</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>4113</v>
+        <v>3883</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>1356</v>
+        <v>1470</v>
       </c>
       <c r="E20" s="22" t="n">
         <v>1.3</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>88.8</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>PRE-PIZZA NINO X 1 UNI</t>
+          <t>PAN DE PANCHOS  NINO  X 6 UN</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>5561545</v>
+        <v>5805610</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>3762</v>
+        <v>4213</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>1452</v>
+        <v>1363</v>
       </c>
       <c r="E21" s="22" t="n">
         <v>1.3</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>90.2</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3336,19 +3367,19 @@
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>5318320</v>
+        <v>5446910</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>3637</v>
+        <v>3714</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>1451</v>
+        <v>1456</v>
       </c>
       <c r="E22" s="22" t="n">
         <v>1.3</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>91.40000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="23">
@@ -3370,7 +3401,7 @@
         <v>1.1</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="24">
@@ -3380,19 +3411,19 @@
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>3497015</v>
+        <v>3562850</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>2146</v>
+        <v>2179</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="E24" s="22" t="n">
         <v>0.8</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3414,7 +3445,7 @@
         <v>0.7</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26">
@@ -3436,7 +3467,7 @@
         <v>0.7</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>94.8</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="27">
@@ -3446,19 +3477,19 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>2559630</v>
+        <v>2617485</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1556</v>
+        <v>1585</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="E27" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>95.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3468,19 +3499,19 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2369070</v>
+        <v>2439000</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>14171</v>
+        <v>14504</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E28" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3490,19 +3521,19 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2262226</v>
+        <v>2372578</v>
       </c>
       <c r="C29" s="32" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5752</v>
+        <v>5786</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>96.5</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="30">
@@ -3524,7 +3555,7 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="31">
@@ -3534,19 +3565,19 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1795250</v>
+        <v>1940750</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>765</v>
+        <v>815</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>2349</v>
+        <v>2383</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>97.5</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3556,255 +3587,255 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>1511153</v>
+        <v>1633093</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>2456</v>
+        <v>2474</v>
       </c>
       <c r="E32" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>FAC.ESPECIALES X 1 U</t>
+          <t>ROSCA NINO CON CHIP DE CHOCOLATE</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>1381370</v>
+        <v>1556100</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>3561</v>
+        <v>399</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>382</v>
+        <v>3842</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>98.2</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>SACRAMENTOS DE OFERTA X 6</t>
+          <t>FAC.ESPECIALES X 1 U</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>1259850</v>
+        <v>1381370</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>899</v>
+        <v>3561</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1371</v>
+        <v>382</v>
       </c>
       <c r="E34" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TORTAS NINOX 12U.</t>
+          <t>SACRAMENTOS DE OFERTA X 6</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>1059900</v>
+        <v>1259850</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>320</v>
+        <v>899</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>3289</v>
+        <v>1371</v>
       </c>
       <c r="E35" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>TORTA MATERA NINO</t>
+          <t>TORTAS NINOX 12U.</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>832710</v>
+        <v>1059900</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>183</v>
+        <v>320</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>7681</v>
+        <v>3289</v>
       </c>
       <c r="E36" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SACRAMENTO X 1</t>
+          <t>TORTA MATERA NINO</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>752020</v>
+        <v>832710</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>2795</v>
+        <v>183</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>268</v>
+        <v>7681</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PAN DULCE NINO CLASICO ECONOMICO</t>
+          <t>SACRAMENTO X 1</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>698010</v>
+        <v>752020</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>439</v>
+        <v>2795</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1547</v>
+        <v>268</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>SACRAMENTO X 12</t>
+          <t>PAN DULCE NINO CLASICO ECONOMICO</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>481150</v>
+        <v>698010</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>154</v>
+        <v>439</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>3118</v>
+        <v>1547</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>SURE PAN DE MIGA X50 PARA 100 SANDWICHS</t>
+          <t>SACRAMENTO X 12</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>442000</v>
-      </c>
-      <c r="C40" s="32" t="n">
-        <v>34</v>
+        <v>481150</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>154</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>13000</v>
+        <v>3118</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>MINIFACTURAS NINO</t>
+          <t>SURE PAN DE MIGA X50 PARA 100 SANDWICHS</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>399216</v>
+        <v>442000</v>
       </c>
       <c r="C41" s="32" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>4558</v>
+        <v>13000</v>
       </c>
       <c r="E41" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>FAC. ESPECIALES X 12U</t>
+          <t>MINIFACTURAS NINO</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>374760</v>
+        <v>399216</v>
       </c>
       <c r="C42" s="32" t="n">
         <v>85</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4425</v>
+        <v>4558</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PAN MIÑON SEPARADO NINO</t>
+          <t>FAC. ESPECIALES X 12U</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>331640</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>120</v>
+        <v>374760</v>
+      </c>
+      <c r="C43" s="32" t="n">
+        <v>85</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>2451</v>
+        <v>4425</v>
       </c>
       <c r="E43" s="6" t="n">
         <v>0.1</v>
@@ -3816,83 +3847,83 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>ARCOR PAN DULCE C/CHIPS X 400GRS</t>
+          <t>PAN MIÑON SEPARADO NINO</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>256392</v>
-      </c>
-      <c r="C44" s="32" t="n">
-        <v>42</v>
+        <v>331640</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>120</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>5827</v>
+        <v>2451</v>
       </c>
       <c r="E44" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>ARCOR PAN DULCE C/ALMENDRAS X 400GRS</t>
+          <t>ARCOR PAN DULCE C/CHIPS X 400GRS</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>211752</v>
+        <v>256392</v>
       </c>
       <c r="C45" s="32" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5882</v>
+        <v>5827</v>
       </c>
       <c r="E45" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>MINI DONAS NINO</t>
+          <t>ARCOR PAN DULCE C/ALMENDRAS X 400GRS</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>181419</v>
+        <v>211752</v>
       </c>
       <c r="C46" s="32" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>15041</v>
+        <v>5882</v>
       </c>
       <c r="E46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ARCOR PAN DULCE C/FRUTAS X 600GRS</t>
+          <t>MINI DONAS NINO</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>95232</v>
+        <v>181419</v>
       </c>
       <c r="C47" s="32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>7936</v>
+        <v>15041</v>
       </c>
       <c r="E47" s="6" t="n">
         <v>0</v>
@@ -3904,17 +3935,17 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>PAN NINO PECETO SABORIZADO</t>
+          <t>ARCOR PAN DULCE C/FRUTAS X 600GRS</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>77655</v>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>471</v>
+        <v>95232</v>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>12</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>170</v>
+        <v>7936</v>
       </c>
       <c r="E48" s="6" t="n">
         <v>0</v>
@@ -3926,61 +3957,61 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>SOPAIPILLAS NINO</t>
+          <t>PAN NINO PECETO SABORIZADO</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>76760</v>
+        <v>77655</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="E49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>ARCOR PAN DULCE C/FRUTOS SECOS CAJAX700G</t>
+          <t>SOPAIPILLAS NINO</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>60685</v>
-      </c>
-      <c r="C50" s="32" t="n">
-        <v>5</v>
+        <v>76760</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>202</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>12137</v>
+        <v>380</v>
       </c>
       <c r="E50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>PIZZETITAS NINO</t>
+          <t>ARCOR PAN DULCE C/FRUTOS SECOS CAJAX700G</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>44040</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>294</v>
+        <v>60685</v>
+      </c>
+      <c r="C51" s="32" t="n">
+        <v>5</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>144</v>
+        <v>12137</v>
       </c>
       <c r="E51" s="6" t="n">
         <v>0</v>
@@ -3992,17 +4023,17 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>WAFFLES NINO</t>
+          <t>PIZZETITAS NINO</t>
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>40784</v>
-      </c>
-      <c r="C52" s="32" t="n">
-        <v>3</v>
+        <v>44040</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>294</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>15900</v>
+        <v>144</v>
       </c>
       <c r="E52" s="6" t="n">
         <v>0</v>
@@ -4014,17 +4045,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>TARTA BANANA SPLIT  NINO</t>
+          <t>WAFFLES NINO</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>15325</v>
+        <v>40784</v>
       </c>
       <c r="C53" s="32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>14595</v>
+        <v>15900</v>
       </c>
       <c r="E53" s="6" t="n">
         <v>0</v>
@@ -4036,17 +4067,17 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>MINI LIBRE REPOSTER</t>
+          <t>PAN CIABATTA X 2 U</t>
         </is>
       </c>
       <c r="B54" s="6" t="n">
-        <v>11200</v>
+        <v>39900</v>
       </c>
       <c r="C54" s="32" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1600</v>
+        <v>2100</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>0</v>
@@ -4058,17 +4089,17 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>PAN CIABATTA NINO</t>
+          <t>TARTA BANANA SPLIT  NINO</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>9900</v>
+        <v>15325</v>
       </c>
       <c r="C55" s="32" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>10000</v>
+        <v>14595</v>
       </c>
       <c r="E55" s="6" t="n">
         <v>0</v>
@@ -4080,17 +4111,17 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>NINO DISCO EMPANADA P/COPETIN 12UN</t>
+          <t>MINI LIBRE REPOSTER</t>
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>6900</v>
+        <v>11200</v>
       </c>
       <c r="C56" s="32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>105</v>
+        <v>1600</v>
       </c>
       <c r="E56" s="6" t="n">
         <v>0</v>
@@ -4102,17 +4133,17 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>PAN CIABATTA X 2 U</t>
+          <t>PAN CIABATTA NINO</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>4200</v>
+        <v>9900</v>
       </c>
       <c r="C57" s="32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>2100</v>
+        <v>10000</v>
       </c>
       <c r="E57" s="6" t="n">
         <v>0</v>
@@ -4124,17 +4155,17 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>TORTA CHOCOTORTA ESPECIAL NINO</t>
+          <t>NINO DISCO EMPANADA P/COPETIN 12UN</t>
         </is>
       </c>
       <c r="B58" s="6" t="n">
-        <v>231</v>
+        <v>6900</v>
       </c>
       <c r="C58" s="32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>23100</v>
+        <v>105</v>
       </c>
       <c r="E58" s="6" t="n">
         <v>0</v>
@@ -4146,17 +4177,17 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TORTAS SURTIDAS X 6 UNI.</t>
-        </is>
-      </c>
-      <c r="B59" s="32" t="n">
-        <v>0</v>
+          <t>TORTA CHOCOTORTA ESPECIAL NINO</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>231</v>
       </c>
       <c r="C59" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="32" t="n">
-        <v>0</v>
+      <c r="D59" s="6" t="n">
+        <v>23100</v>
       </c>
       <c r="E59" s="6" t="n">
         <v>0</v>
@@ -4165,8 +4196,30 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>TORTAS SURTIDAS X 6 UNI.</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Verde = Core (80%) | Amarillo = Complementario (80-95%) | Sin color = Marginal</t>
         </is>
@@ -4174,8 +4227,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A61:F61"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A62:F62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6315,11 +6368,11 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>7051850</v>
+        <v>3671076</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F6" s="33" t="inlineStr">
@@ -6345,11 +6398,11 @@
         </is>
       </c>
       <c r="D7" s="34" t="n">
-        <v>9694107</v>
+        <v>5627885</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F7" s="33" t="inlineStr">
@@ -6375,11 +6428,11 @@
         </is>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12042779</v>
+        <v>7367270</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F8" s="33" t="inlineStr">
@@ -6405,11 +6458,11 @@
         </is>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13804283</v>
+        <v>8671809</v>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F9" s="33" t="inlineStr">
@@ -6435,11 +6488,11 @@
         </is>
       </c>
       <c r="D10" s="34" t="n">
-        <v>15565787</v>
+        <v>9976349</v>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F10" s="33" t="inlineStr">
@@ -6504,11 +6557,11 @@
         </is>
       </c>
       <c r="D15" s="34" t="n">
-        <v>13483332</v>
+        <v>13480037</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>218%</t>
+          <t>161%</t>
         </is>
       </c>
       <c r="F15" s="33" t="inlineStr">
@@ -6534,11 +6587,11 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>11211750</v>
+        <v>11209472</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>262%</t>
+          <t>194%</t>
         </is>
       </c>
       <c r="F16" s="33" t="inlineStr">
@@ -6564,11 +6617,11 @@
         </is>
       </c>
       <c r="D17" s="34" t="n">
-        <v>9751433</v>
+        <v>9749709</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t>301%</t>
+          <t>223%</t>
         </is>
       </c>
       <c r="F17" s="33" t="inlineStr">
@@ -6594,11 +6647,11 @@
         </is>
       </c>
       <c r="D18" s="34" t="n">
-        <v>8883622</v>
+        <v>8882192</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>330%</t>
+          <t>245%</t>
         </is>
       </c>
       <c r="F18" s="33" t="inlineStr">
@@ -6624,11 +6677,11 @@
         </is>
       </c>
       <c r="D19" s="34" t="n">
-        <v>8157647</v>
+        <v>8156440</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
-          <t>360%</t>
+          <t>267%</t>
         </is>
       </c>
       <c r="F19" s="33" t="inlineStr">
@@ -6682,13 +6735,13 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>29358404</v>
+        <v>21742317</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>11050346</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>18308058</v>
+        <v>10691971</v>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
